--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/143.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/143.xlsx
@@ -426,13 +426,13 @@
         <v>-14.04267866857557</v>
       </c>
       <c r="E2">
-        <v>-14.87835064168889</v>
+        <v>-15.91962717220461</v>
       </c>
       <c r="F2">
-        <v>-0.5286170067721927</v>
+        <v>-1.539647705563017</v>
       </c>
       <c r="G2">
-        <v>-10.34637374355139</v>
+        <v>-8.513601017027067</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.82849859294394</v>
       </c>
       <c r="E3">
-        <v>-14.73807177598148</v>
+        <v>-15.36525652456649</v>
       </c>
       <c r="F3">
-        <v>-0.7912152720314556</v>
+        <v>-1.346517159069924</v>
       </c>
       <c r="G3">
-        <v>-9.582639574590067</v>
+        <v>-8.226762424918336</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.57348355064257</v>
       </c>
       <c r="E4">
-        <v>-16.29395195570008</v>
+        <v>-16.03028948795466</v>
       </c>
       <c r="F4">
-        <v>-0.5301370609563297</v>
+        <v>-1.332989919382208</v>
       </c>
       <c r="G4">
-        <v>-9.263597447949953</v>
+        <v>-8.343705507388075</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.29146218632358</v>
       </c>
       <c r="E5">
-        <v>-17.27391462742735</v>
+        <v>-16.59574090340742</v>
       </c>
       <c r="F5">
-        <v>0.006350117262353258</v>
+        <v>-1.025947257860543</v>
       </c>
       <c r="G5">
-        <v>-9.440129470339556</v>
+        <v>-8.908110632190196</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.99576992434062</v>
       </c>
       <c r="E6">
-        <v>-16.83191741860512</v>
+        <v>-17.45586681556809</v>
       </c>
       <c r="F6">
-        <v>0.299229352930952</v>
+        <v>-0.6610099985572209</v>
       </c>
       <c r="G6">
-        <v>-9.36760559634302</v>
+        <v>-8.380634489629372</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.71191468384491</v>
       </c>
       <c r="E7">
-        <v>-18.29740710705014</v>
+        <v>-17.6536385856451</v>
       </c>
       <c r="F7">
-        <v>-0.2915614503782525</v>
+        <v>-0.7841741491076597</v>
       </c>
       <c r="G7">
-        <v>-9.259600397980959</v>
+        <v>-7.978359214679976</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.43180202659165</v>
       </c>
       <c r="E8">
-        <v>-19.5745154362236</v>
+        <v>-18.0688683474788</v>
       </c>
       <c r="F8">
-        <v>-0.5679992498360867</v>
+        <v>-0.6038079159243038</v>
       </c>
       <c r="G8">
-        <v>-9.53252241604676</v>
+        <v>-8.023223555105963</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.18648499210593</v>
       </c>
       <c r="E9">
-        <v>-19.582946455213</v>
+        <v>-18.18137884226841</v>
       </c>
       <c r="F9">
-        <v>-0.08453255560098891</v>
+        <v>-0.2932471780429495</v>
       </c>
       <c r="G9">
-        <v>-9.734939971057251</v>
+        <v>-8.179360440749788</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.96888637226222</v>
       </c>
       <c r="E10">
-        <v>-19.50281024270043</v>
+        <v>-18.62870462122039</v>
       </c>
       <c r="F10">
-        <v>0.3452070572559358</v>
+        <v>-0.0770060093791526</v>
       </c>
       <c r="G10">
-        <v>-9.255042037924875</v>
+        <v>-8.399456652759003</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.79282715734738</v>
       </c>
       <c r="E11">
-        <v>-21.28217057059672</v>
+        <v>-19.85210362154116</v>
       </c>
       <c r="F11">
-        <v>0.6278783214198363</v>
+        <v>0.2222309461059324</v>
       </c>
       <c r="G11">
-        <v>-8.81033041501923</v>
+        <v>-7.64211750267361</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.67286026968737</v>
       </c>
       <c r="E12">
-        <v>-21.02841766507235</v>
+        <v>-20.34297582123397</v>
       </c>
       <c r="F12">
-        <v>1.2765347296516</v>
+        <v>0.1820642391115872</v>
       </c>
       <c r="G12">
-        <v>-9.375843800900277</v>
+        <v>-7.564622770975594</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.60021536476297</v>
       </c>
       <c r="E13">
-        <v>-21.79768792629106</v>
+        <v>-20.71276945117405</v>
       </c>
       <c r="F13">
-        <v>1.094418156146129</v>
+        <v>0.6808275658067807</v>
       </c>
       <c r="G13">
-        <v>-8.893806362575486</v>
+        <v>-7.278388566239706</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.60420701472084</v>
       </c>
       <c r="E14">
-        <v>-21.45601153702007</v>
+        <v>-21.98687500855966</v>
       </c>
       <c r="F14">
-        <v>1.579761930915971</v>
+        <v>1.035004332547737</v>
       </c>
       <c r="G14">
-        <v>-9.651149428777765</v>
+        <v>-7.286327840541282</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.67167877418571</v>
       </c>
       <c r="E15">
-        <v>-23.39654969001031</v>
+        <v>-23.66948212543274</v>
       </c>
       <c r="F15">
-        <v>2.001354550366362</v>
+        <v>1.379764218653669</v>
       </c>
       <c r="G15">
-        <v>-8.022482103642087</v>
+        <v>-6.983638112647608</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.81075803333367</v>
       </c>
       <c r="E16">
-        <v>-24.03240634384156</v>
+        <v>-22.96197426982555</v>
       </c>
       <c r="F16">
-        <v>1.703952428678478</v>
+        <v>1.739288925347099</v>
       </c>
       <c r="G16">
-        <v>-7.237224956271623</v>
+        <v>-6.751065152237463</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.01638714259353</v>
       </c>
       <c r="E17">
-        <v>-24.14926109767693</v>
+        <v>-24.24260036899113</v>
       </c>
       <c r="F17">
-        <v>2.09177416585154</v>
+        <v>2.051752423152684</v>
       </c>
       <c r="G17">
-        <v>-7.541003364659792</v>
+        <v>-7.084214437275656</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.26085794023654</v>
       </c>
       <c r="E18">
-        <v>-24.28819016970377</v>
+        <v>-25.20392342829257</v>
       </c>
       <c r="F18">
-        <v>2.694714633857604</v>
+        <v>2.676217189753091</v>
       </c>
       <c r="G18">
-        <v>-6.801186226897656</v>
+        <v>-6.77579934649367</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.54246604591681</v>
       </c>
       <c r="E19">
-        <v>-26.03829527702797</v>
+        <v>-26.17974950154031</v>
       </c>
       <c r="F19">
-        <v>2.522374452439973</v>
+        <v>3.044433127236694</v>
       </c>
       <c r="G19">
-        <v>-6.703361627068641</v>
+        <v>-6.531705170202943</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.81815151318857</v>
       </c>
       <c r="E20">
-        <v>-26.19374167049366</v>
+        <v>-26.89459608155848</v>
       </c>
       <c r="F20">
-        <v>3.319389805778323</v>
+        <v>3.426042108888759</v>
       </c>
       <c r="G20">
-        <v>-7.209840856255436</v>
+        <v>-6.2487187317384</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.07269977894601</v>
       </c>
       <c r="E21">
-        <v>-27.37143458018469</v>
+        <v>-27.39623755821657</v>
       </c>
       <c r="F21">
-        <v>3.679113320648425</v>
+        <v>3.836491530036692</v>
       </c>
       <c r="G21">
-        <v>-5.863722669865289</v>
+        <v>-5.533818540353849</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.28047521255119</v>
       </c>
       <c r="E22">
-        <v>-27.99115600801898</v>
+        <v>-28.21518853330288</v>
       </c>
       <c r="F22">
-        <v>3.740024832511078</v>
+        <v>4.070631233172778</v>
       </c>
       <c r="G22">
-        <v>-6.611821089470436</v>
+        <v>-6.059309211653131</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.41379101165127</v>
       </c>
       <c r="E23">
-        <v>-28.57239170311175</v>
+        <v>-28.31416786559619</v>
       </c>
       <c r="F23">
-        <v>4.312367065392535</v>
+        <v>4.263306177594331</v>
       </c>
       <c r="G23">
-        <v>-6.682940382876953</v>
+        <v>-5.322105429226699</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.47595695356042</v>
       </c>
       <c r="E24">
-        <v>-28.24233392252196</v>
+        <v>-28.89128980487172</v>
       </c>
       <c r="F24">
-        <v>4.688293446661396</v>
+        <v>4.477521987958283</v>
       </c>
       <c r="G24">
-        <v>-6.731662098436309</v>
+        <v>-5.493965524170505</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.44437321191892</v>
       </c>
       <c r="E25">
-        <v>-30.43667274296681</v>
+        <v>-28.59512638190386</v>
       </c>
       <c r="F25">
-        <v>4.971735920877302</v>
+        <v>4.407836408565178</v>
       </c>
       <c r="G25">
-        <v>-6.354592257141817</v>
+        <v>-5.41389398756106</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.33180279755418</v>
       </c>
       <c r="E26">
-        <v>-28.74832796464847</v>
+        <v>-29.3306871034046</v>
       </c>
       <c r="F26">
-        <v>4.607582297137029</v>
+        <v>4.360390837202433</v>
       </c>
       <c r="G26">
-        <v>-5.568063677155482</v>
+        <v>-5.810526138076764</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.13881137956512</v>
       </c>
       <c r="E27">
-        <v>-28.44907870566626</v>
+        <v>-29.40517287190974</v>
       </c>
       <c r="F27">
-        <v>4.185426387852733</v>
+        <v>4.344627005527159</v>
       </c>
       <c r="G27">
-        <v>-6.969963032479357</v>
+        <v>-5.823475431248686</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.86797439681416</v>
       </c>
       <c r="E28">
-        <v>-29.57375379619019</v>
+        <v>-29.74630311389152</v>
       </c>
       <c r="F28">
-        <v>4.387395614533697</v>
+        <v>4.202000362847945</v>
       </c>
       <c r="G28">
-        <v>-6.497170240751696</v>
+        <v>-5.438941471168201</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.54047794194313</v>
       </c>
       <c r="E29">
-        <v>-29.03274402938406</v>
+        <v>-29.70491220982828</v>
       </c>
       <c r="F29">
-        <v>4.497744092995426</v>
+        <v>3.779375597613666</v>
       </c>
       <c r="G29">
-        <v>-6.081604970461239</v>
+        <v>-5.611195788545265</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.15022292291072</v>
       </c>
       <c r="E30">
-        <v>-29.99985043545531</v>
+        <v>-29.81659621556424</v>
       </c>
       <c r="F30">
-        <v>3.670243162499248</v>
+        <v>3.871627561793836</v>
       </c>
       <c r="G30">
-        <v>-6.337708571871087</v>
+        <v>-5.153028388017021</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.71943306355267</v>
       </c>
       <c r="E31">
-        <v>-28.22976422844737</v>
+        <v>-29.19845508463905</v>
       </c>
       <c r="F31">
-        <v>3.243922221913677</v>
+        <v>3.437511683947921</v>
       </c>
       <c r="G31">
-        <v>-5.793261284095732</v>
+        <v>-4.675865209843836</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.25023072268474</v>
       </c>
       <c r="E32">
-        <v>-29.45165976626855</v>
+        <v>-28.71557158692955</v>
       </c>
       <c r="F32">
-        <v>3.325456768636426</v>
+        <v>3.420003310522351</v>
       </c>
       <c r="G32">
-        <v>-6.025118900487912</v>
+        <v>-4.630845530114679</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.74780135375423</v>
       </c>
       <c r="E33">
-        <v>-27.90178305351999</v>
+        <v>-28.97231688121346</v>
       </c>
       <c r="F33">
-        <v>3.083122855151848</v>
+        <v>3.00170427986549</v>
       </c>
       <c r="G33">
-        <v>-6.053821426522611</v>
+        <v>-4.907869027933119</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.22858004228592</v>
       </c>
       <c r="E34">
-        <v>-28.05403147426556</v>
+        <v>-29.24547774325876</v>
       </c>
       <c r="F34">
-        <v>3.448181056095979</v>
+        <v>3.091553978577541</v>
       </c>
       <c r="G34">
-        <v>-5.981200954976204</v>
+        <v>-4.406308441555981</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.686039190066648</v>
       </c>
       <c r="E35">
-        <v>-26.79193285082004</v>
+        <v>-28.69975200499328</v>
       </c>
       <c r="F35">
-        <v>2.947432961103678</v>
+        <v>2.802649249707574</v>
       </c>
       <c r="G35">
-        <v>-4.415122315295579</v>
+        <v>-4.455291231574448</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.141848696212428</v>
       </c>
       <c r="E36">
-        <v>-29.99689334899204</v>
+        <v>-28.03552891781345</v>
       </c>
       <c r="F36">
-        <v>3.167294923685111</v>
+        <v>2.794125349132767</v>
       </c>
       <c r="G36">
-        <v>-4.918899423830572</v>
+        <v>-3.732373443550589</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.597284729104306</v>
       </c>
       <c r="E37">
-        <v>-26.12575775431754</v>
+        <v>-26.93913927301726</v>
       </c>
       <c r="F37">
-        <v>3.145699385494128</v>
+        <v>2.849558038993305</v>
       </c>
       <c r="G37">
-        <v>-5.046290706153945</v>
+        <v>-3.111794232753778</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.062438846694265</v>
       </c>
       <c r="E38">
-        <v>-27.53483022012609</v>
+        <v>-27.2016180755351</v>
       </c>
       <c r="F38">
-        <v>2.922010365511761</v>
+        <v>2.614560147227919</v>
       </c>
       <c r="G38">
-        <v>-4.583606717483075</v>
+        <v>-2.806472874312262</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.553279267626533</v>
       </c>
       <c r="E39">
-        <v>-27.48475495118263</v>
+        <v>-27.19295862992283</v>
       </c>
       <c r="F39">
-        <v>3.198333850268009</v>
+        <v>2.566067519468036</v>
       </c>
       <c r="G39">
-        <v>-4.109524217927405</v>
+        <v>-2.398275125257926</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.065746616251013</v>
       </c>
       <c r="E40">
-        <v>-26.91677838324438</v>
+        <v>-26.10455976371561</v>
       </c>
       <c r="F40">
-        <v>2.638289559848513</v>
+        <v>2.473146234426404</v>
       </c>
       <c r="G40">
-        <v>-4.314076056641131</v>
+        <v>-2.160143889613301</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.619393665835521</v>
       </c>
       <c r="E41">
-        <v>-26.47738523792282</v>
+        <v>-26.86733855563362</v>
       </c>
       <c r="F41">
-        <v>3.022845872719739</v>
+        <v>2.615204617067297</v>
       </c>
       <c r="G41">
-        <v>-2.939887144407333</v>
+        <v>-1.7479699765467</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.210507140126955</v>
       </c>
       <c r="E42">
-        <v>-25.12297318636034</v>
+        <v>-25.46561312065869</v>
       </c>
       <c r="F42">
-        <v>2.754703344433539</v>
+        <v>2.744357035572573</v>
       </c>
       <c r="G42">
-        <v>-3.687531294453627</v>
+        <v>-1.183124941280976</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.843999756260717</v>
       </c>
       <c r="E43">
-        <v>-25.625964456699</v>
+        <v>-25.68144305357606</v>
       </c>
       <c r="F43">
-        <v>2.908083852735896</v>
+        <v>2.320584153118013</v>
       </c>
       <c r="G43">
-        <v>-4.136012832548841</v>
+        <v>-0.9569300299069212</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.524245247657533</v>
       </c>
       <c r="E44">
-        <v>-25.07252828160897</v>
+        <v>-24.77920773179295</v>
       </c>
       <c r="F44">
-        <v>3.015145369343315</v>
+        <v>2.525568637145168</v>
       </c>
       <c r="G44">
-        <v>-2.790998991120734</v>
+        <v>-1.052861839907379</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.239687501241742</v>
       </c>
       <c r="E45">
-        <v>-24.3378085854015</v>
+        <v>-24.57342857028167</v>
       </c>
       <c r="F45">
-        <v>2.911521577457513</v>
+        <v>2.545852041370116</v>
       </c>
       <c r="G45">
-        <v>-3.027696927984837</v>
+        <v>-0.8644966176585553</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.999294439235872</v>
       </c>
       <c r="E46">
-        <v>-24.11826152834842</v>
+        <v>-24.5745042520148</v>
       </c>
       <c r="F46">
-        <v>2.854677349542606</v>
+        <v>2.239627806842418</v>
       </c>
       <c r="G46">
-        <v>-3.276741076020316</v>
+        <v>-0.4779341090307756</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.791125693352154</v>
       </c>
       <c r="E47">
-        <v>-23.2840724209113</v>
+        <v>-23.55602469846108</v>
       </c>
       <c r="F47">
-        <v>2.509581146271137</v>
+        <v>2.524402295842026</v>
       </c>
       <c r="G47">
-        <v>-1.905131579442538</v>
+        <v>-0.4581394435409547</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.615416050664092</v>
       </c>
       <c r="E48">
-        <v>-22.89155241860176</v>
+        <v>-23.30750483920599</v>
       </c>
       <c r="F48">
-        <v>2.670247974248518</v>
+        <v>1.957398062504209</v>
       </c>
       <c r="G48">
-        <v>-2.429481355355503</v>
+        <v>-0.2386384812985141</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.470522919284772</v>
       </c>
       <c r="E49">
-        <v>-22.96278414603389</v>
+        <v>-23.25104608445627</v>
       </c>
       <c r="F49">
-        <v>2.225517396503131</v>
+        <v>2.380254770611273</v>
       </c>
       <c r="G49">
-        <v>-1.704229561667188</v>
+        <v>0.1159345738543546</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.34701332134695</v>
       </c>
       <c r="E50">
-        <v>-21.55248648288451</v>
+        <v>-22.82870187162313</v>
       </c>
       <c r="F50">
-        <v>2.163227481282219</v>
+        <v>1.940005660515031</v>
       </c>
       <c r="G50">
-        <v>-2.210878489252406</v>
+        <v>0.06612417780050422</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.253569251077695</v>
       </c>
       <c r="E51">
-        <v>-22.44983762814962</v>
+        <v>-22.25168791584205</v>
       </c>
       <c r="F51">
-        <v>2.512195473794372</v>
+        <v>1.90147663587602</v>
       </c>
       <c r="G51">
-        <v>-2.263140374477311</v>
+        <v>0.7295718147833946</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.182968080483082</v>
       </c>
       <c r="E52">
-        <v>-22.02015884411683</v>
+        <v>-22.23173588863757</v>
       </c>
       <c r="F52">
-        <v>2.291082676434712</v>
+        <v>1.887215462669424</v>
       </c>
       <c r="G52">
-        <v>-2.912252412910399</v>
+        <v>0.5352201551871483</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.143449373126017</v>
       </c>
       <c r="E53">
-        <v>-20.60344031625927</v>
+        <v>-22.05822717912021</v>
       </c>
       <c r="F53">
-        <v>2.427551235841513</v>
+        <v>2.111346830844886</v>
       </c>
       <c r="G53">
-        <v>-1.599846771425297</v>
+        <v>0.8338136248173659</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.139627211565676</v>
       </c>
       <c r="E54">
-        <v>-20.70657285987741</v>
+        <v>-21.39110099722433</v>
       </c>
       <c r="F54">
-        <v>2.340264505873724</v>
+        <v>1.694061721889052</v>
       </c>
       <c r="G54">
-        <v>-1.952709788870986</v>
+        <v>0.7129544254609586</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.17154218107818</v>
       </c>
       <c r="E55">
-        <v>-20.70429274686008</v>
+        <v>-21.59323363919241</v>
       </c>
       <c r="F55">
-        <v>2.545497500121718</v>
+        <v>1.732216324461997</v>
       </c>
       <c r="G55">
-        <v>-1.430534763202418</v>
+        <v>0.5062487224595642</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.251771897615898</v>
       </c>
       <c r="E56">
-        <v>-21.29825595805778</v>
+        <v>-21.0155967017126</v>
       </c>
       <c r="F56">
-        <v>2.148668095810615</v>
+        <v>2.133744228681779</v>
       </c>
       <c r="G56">
-        <v>-2.209998668325201</v>
+        <v>0.9293224941940632</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.374502768238123</v>
       </c>
       <c r="E57">
-        <v>-20.40492927456644</v>
+        <v>-21.25206394170304</v>
       </c>
       <c r="F57">
-        <v>2.694966457548055</v>
+        <v>1.924442293751234</v>
       </c>
       <c r="G57">
-        <v>-2.035577432937513</v>
+        <v>0.3804813232718638</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.547506156322519</v>
       </c>
       <c r="E58">
-        <v>-19.88274186148442</v>
+        <v>-20.94823992044653</v>
       </c>
       <c r="F58">
-        <v>1.998700461207793</v>
+        <v>2.046134435426898</v>
       </c>
       <c r="G58">
-        <v>-2.377472712355936</v>
+        <v>0.5123552540581782</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.767099803435278</v>
       </c>
       <c r="E59">
-        <v>-20.17497426993333</v>
+        <v>-20.28494715260347</v>
       </c>
       <c r="F59">
-        <v>1.819612398926956</v>
+        <v>1.878641860050449</v>
       </c>
       <c r="G59">
-        <v>-2.264813861760215</v>
+        <v>0.0232818590603352</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.024030062323043</v>
       </c>
       <c r="E60">
-        <v>-20.24419584308425</v>
+        <v>-20.72677407976138</v>
       </c>
       <c r="F60">
-        <v>2.006480487854886</v>
+        <v>2.272012002087461</v>
       </c>
       <c r="G60">
-        <v>-2.578265078858458</v>
+        <v>0.283325074058174</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.315705763971287</v>
       </c>
       <c r="E61">
-        <v>-18.92560939240974</v>
+        <v>-20.28522957097356</v>
       </c>
       <c r="F61">
-        <v>1.941741918591299</v>
+        <v>2.037436577697503</v>
       </c>
       <c r="G61">
-        <v>-2.321258159820085</v>
+        <v>-0.2844935992968278</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.61993606465291</v>
       </c>
       <c r="E62">
-        <v>-19.90437593927545</v>
+        <v>-20.03627777774068</v>
       </c>
       <c r="F62">
-        <v>2.033904419091966</v>
+        <v>1.695597515053842</v>
       </c>
       <c r="G62">
-        <v>-3.834931323323292</v>
+        <v>-0.6323857590410376</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.929762413875157</v>
       </c>
       <c r="E63">
-        <v>-18.16772308343237</v>
+        <v>-20.17868308764641</v>
       </c>
       <c r="F63">
-        <v>2.507773648598229</v>
+        <v>1.907144325645974</v>
       </c>
       <c r="G63">
-        <v>-3.019882969423635</v>
+        <v>-1.042327485482237</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.227267233645638</v>
       </c>
       <c r="E64">
-        <v>-19.08284166674509</v>
+        <v>-19.2194740129093</v>
       </c>
       <c r="F64">
-        <v>2.511052326778509</v>
+        <v>1.880300251590854</v>
       </c>
       <c r="G64">
-        <v>-3.251147946793632</v>
+        <v>-1.336610615792526</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.496941170839769</v>
       </c>
       <c r="E65">
-        <v>-19.6186599193952</v>
+        <v>-19.18838307293164</v>
       </c>
       <c r="F65">
-        <v>1.979909775042689</v>
+        <v>1.963074035948192</v>
       </c>
       <c r="G65">
-        <v>-4.287670985846611</v>
+        <v>-1.018470501408644</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.73231886932085</v>
       </c>
       <c r="E66">
-        <v>-20.55877668167206</v>
+        <v>-19.54175905850467</v>
       </c>
       <c r="F66">
-        <v>1.349311776191954</v>
+        <v>2.044640060632247</v>
       </c>
       <c r="G66">
-        <v>-3.691888627176195</v>
+        <v>-1.027018079199949</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.915767514357874</v>
       </c>
       <c r="E67">
-        <v>-20.14709376230976</v>
+        <v>-18.71837245372344</v>
       </c>
       <c r="F67">
-        <v>1.765934191225548</v>
+        <v>1.736875062735342</v>
       </c>
       <c r="G67">
-        <v>-2.627464560677988</v>
+        <v>-1.475201992411775</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.048384116536122</v>
       </c>
       <c r="E68">
-        <v>-18.27916204970017</v>
+        <v>-18.36300292671449</v>
       </c>
       <c r="F68">
-        <v>1.954929527643867</v>
+        <v>1.742299212488873</v>
       </c>
       <c r="G68">
-        <v>-3.459824761961317</v>
+        <v>-1.545924452640443</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.122776386645771</v>
       </c>
       <c r="E69">
-        <v>-18.05277050038377</v>
+        <v>-18.64077385333034</v>
       </c>
       <c r="F69">
-        <v>1.542437352480631</v>
+        <v>1.51422647221089</v>
       </c>
       <c r="G69">
-        <v>-3.355844026386457</v>
+        <v>-1.797010202946172</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.138341162602359</v>
       </c>
       <c r="E70">
-        <v>-17.6655499957247</v>
+        <v>-18.88733755005144</v>
       </c>
       <c r="F70">
-        <v>1.735286254056772</v>
+        <v>1.666811747806559</v>
       </c>
       <c r="G70">
-        <v>-3.373570982160116</v>
+        <v>-1.736503586302531</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.102708272215821</v>
       </c>
       <c r="E71">
-        <v>-18.14254216316994</v>
+        <v>-18.5291770650322</v>
       </c>
       <c r="F71">
-        <v>1.789880636105676</v>
+        <v>1.699520663073501</v>
       </c>
       <c r="G71">
-        <v>-3.427631670408299</v>
+        <v>-1.440476478605377</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.014269292036693</v>
       </c>
       <c r="E72">
-        <v>-18.79070062894533</v>
+        <v>-18.61841296355747</v>
       </c>
       <c r="F72">
-        <v>1.736923108044704</v>
+        <v>1.777537961803964</v>
       </c>
       <c r="G72">
-        <v>-3.474369220078409</v>
+        <v>-1.376043302096702</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.887406507524608</v>
       </c>
       <c r="E73">
-        <v>-20.18159448878511</v>
+        <v>-18.92291395825992</v>
       </c>
       <c r="F73">
-        <v>1.358127262092546</v>
+        <v>1.605015539557716</v>
       </c>
       <c r="G73">
-        <v>-2.824319924337112</v>
+        <v>-1.611934518882151</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.723221453977407</v>
       </c>
       <c r="E74">
-        <v>-20.03690906586206</v>
+        <v>-18.68375543733099</v>
       </c>
       <c r="F74">
-        <v>1.804840951400235</v>
+        <v>1.533664941684984</v>
       </c>
       <c r="G74">
-        <v>-3.595975092387875</v>
+        <v>-1.513347581632531</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.529198299967856</v>
       </c>
       <c r="E75">
-        <v>-18.34933470824448</v>
+        <v>-19.6053281110425</v>
       </c>
       <c r="F75">
-        <v>1.52470697659111</v>
+        <v>1.467403833135051</v>
       </c>
       <c r="G75">
-        <v>-3.25039083086221</v>
+        <v>-1.687257111080361</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.315471008984804</v>
       </c>
       <c r="E76">
-        <v>-17.95107912109534</v>
+        <v>-18.49992184446011</v>
       </c>
       <c r="F76">
-        <v>1.516028999679382</v>
+        <v>1.498895048319877</v>
       </c>
       <c r="G76">
-        <v>-4.183269920392582</v>
+        <v>-1.427433198628175</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.08187658651402</v>
       </c>
       <c r="E77">
-        <v>-18.10378024187531</v>
+        <v>-19.0838965824216</v>
       </c>
       <c r="F77">
-        <v>1.230006989371158</v>
+        <v>1.208852142638464</v>
       </c>
       <c r="G77">
-        <v>-2.711744617568308</v>
+        <v>-1.629149768715952</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.845686180302655</v>
       </c>
       <c r="E78">
-        <v>-20.11259303583441</v>
+        <v>-19.86302241411413</v>
       </c>
       <c r="F78">
-        <v>0.8208084030014524</v>
+        <v>0.5853466254904985</v>
       </c>
       <c r="G78">
-        <v>-2.265999139804581</v>
+        <v>-0.9338510477214799</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.608943999685407</v>
       </c>
       <c r="E79">
-        <v>-20.1570531630667</v>
+        <v>-19.88188214674018</v>
       </c>
       <c r="F79">
-        <v>0.5598064017273842</v>
+        <v>0.7902217650204835</v>
       </c>
       <c r="G79">
-        <v>-3.481363404838002</v>
+        <v>-0.6954221871934679</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.382797832722</v>
       </c>
       <c r="E80">
-        <v>-19.59953438124436</v>
+        <v>-20.35661081401338</v>
       </c>
       <c r="F80">
-        <v>1.037318791071159</v>
+        <v>0.7672875851065764</v>
       </c>
       <c r="G80">
-        <v>-2.299763899601448</v>
+        <v>-0.4681307630911452</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.176550181005487</v>
       </c>
       <c r="E81">
-        <v>-21.05314173208905</v>
+        <v>-20.32136666271089</v>
       </c>
       <c r="F81">
-        <v>1.06716321185922</v>
+        <v>0.6300420170759486</v>
       </c>
       <c r="G81">
-        <v>-1.63667132388295</v>
+        <v>-0.3655859370413976</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.988556236312715</v>
       </c>
       <c r="E82">
-        <v>-20.21823827230407</v>
+        <v>-20.72703988528617</v>
       </c>
       <c r="F82">
-        <v>-0.4257553128969668</v>
+        <v>0.5817490258601402</v>
       </c>
       <c r="G82">
-        <v>-2.210549535433926</v>
+        <v>-0.6708420268681363</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.831752607961048</v>
       </c>
       <c r="E83">
-        <v>-20.8927156382449</v>
+        <v>-21.57535821765034</v>
       </c>
       <c r="F83">
-        <v>-0.2465545926493498</v>
+        <v>0.4129749661115606</v>
       </c>
       <c r="G83">
-        <v>-1.887832785781821</v>
+        <v>0.0672206905287718</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.700605100678655</v>
       </c>
       <c r="E84">
-        <v>-23.50457886978042</v>
+        <v>-23.32054592276595</v>
       </c>
       <c r="F84">
-        <v>0.3586647140818166</v>
+        <v>0.08841399075549188</v>
       </c>
       <c r="G84">
-        <v>-2.090134162658007</v>
+        <v>-0.2250652201693161</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.599987158202675</v>
       </c>
       <c r="E85">
-        <v>-23.70938202663037</v>
+        <v>-24.15024956197225</v>
       </c>
       <c r="F85">
-        <v>-0.005517902517555259</v>
+        <v>0.2705040565040736</v>
       </c>
       <c r="G85">
-        <v>-1.046710925650716</v>
+        <v>-0.06127493675664189</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.529461433631563</v>
       </c>
       <c r="E86">
-        <v>-24.0966980551499</v>
+        <v>-24.43866101600231</v>
       </c>
       <c r="F86">
-        <v>0.04411207368637152</v>
+        <v>-0.2372487132463001</v>
       </c>
       <c r="G86">
-        <v>-1.063879182081877</v>
+        <v>0.3410956303703288</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.481434174291963</v>
       </c>
       <c r="E87">
-        <v>-24.55775435074177</v>
+        <v>-25.94206121742037</v>
       </c>
       <c r="F87">
-        <v>-0.8509339348340775</v>
+        <v>-0.448899898131185</v>
       </c>
       <c r="G87">
-        <v>-2.384192768933461</v>
+        <v>-0.2763376331941899</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.460508131346937</v>
       </c>
       <c r="E88">
-        <v>-26.15911219446724</v>
+        <v>-26.87637594347645</v>
       </c>
       <c r="F88">
-        <v>-0.9860141504737873</v>
+        <v>-0.7864645849764004</v>
       </c>
       <c r="G88">
-        <v>-1.373730182388975</v>
+        <v>0.1165689847899951</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.455230283515401</v>
       </c>
       <c r="E89">
-        <v>-27.76142527679741</v>
+        <v>-27.82681343589551</v>
       </c>
       <c r="F89">
-        <v>-0.9650274623238618</v>
+        <v>-0.9146792915817078</v>
       </c>
       <c r="G89">
-        <v>-1.704652502290948</v>
+        <v>0.2946818130295168</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.467260204207903</v>
       </c>
       <c r="E90">
-        <v>-29.44782427561007</v>
+        <v>-29.16152888275</v>
       </c>
       <c r="F90">
-        <v>-1.155696929263238</v>
+        <v>-1.349378340079193</v>
       </c>
       <c r="G90">
-        <v>-1.023391754962892</v>
+        <v>0.1423840273069233</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.491859663196843</v>
       </c>
       <c r="E91">
-        <v>-30.53259946493637</v>
+        <v>-31.0381781859304</v>
       </c>
       <c r="F91">
-        <v>-1.081023749737877</v>
+        <v>-1.442095846739736</v>
       </c>
       <c r="G91">
-        <v>-1.873706046799307</v>
+        <v>0.4495407391959925</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.522093407547581</v>
       </c>
       <c r="E92">
-        <v>-32.84131564866134</v>
+        <v>-32.61790195186484</v>
       </c>
       <c r="F92">
-        <v>-1.219410808049562</v>
+        <v>-1.773370739895495</v>
       </c>
       <c r="G92">
-        <v>-2.062188752554731</v>
+        <v>-0.2519167282889163</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.561119660086939</v>
       </c>
       <c r="E93">
-        <v>-33.3324557304846</v>
+        <v>-34.2538518927148</v>
       </c>
       <c r="F93">
-        <v>-1.325011084558443</v>
+        <v>-1.792940919786633</v>
       </c>
       <c r="G93">
-        <v>-2.185462890657918</v>
+        <v>-0.288208688849982</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.598707066212918</v>
       </c>
       <c r="E94">
-        <v>-35.95654809276608</v>
+        <v>-36.84201482382519</v>
       </c>
       <c r="F94">
-        <v>-2.129250630016607</v>
+        <v>-1.994592053384923</v>
       </c>
       <c r="G94">
-        <v>-1.896808525686069</v>
+        <v>0.05698657173160773</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.638287698926034</v>
       </c>
       <c r="E95">
-        <v>-37.68641252469872</v>
+        <v>-38.03696017335955</v>
       </c>
       <c r="F95">
-        <v>-2.276808543844686</v>
+        <v>-2.469221724166955</v>
       </c>
       <c r="G95">
-        <v>-3.18667560911609</v>
+        <v>-0.5447665598186846</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.674629113054369</v>
       </c>
       <c r="E96">
-        <v>-41.04546131623319</v>
+        <v>-40.64386239396757</v>
       </c>
       <c r="F96">
-        <v>-2.060776952133797</v>
+        <v>-2.540427357744198</v>
       </c>
       <c r="G96">
-        <v>-2.463530686312803</v>
+        <v>-0.5045349856696288</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.702826755801668</v>
       </c>
       <c r="E97">
-        <v>-41.29198348084104</v>
+        <v>-42.64835377154319</v>
       </c>
       <c r="F97">
-        <v>-2.903344228952092</v>
+        <v>-3.096740681381484</v>
       </c>
       <c r="G97">
-        <v>-3.26856683470554</v>
+        <v>-1.143117891166756</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.723075971006191</v>
       </c>
       <c r="E98">
-        <v>-43.87670962958013</v>
+        <v>-44.06388655756751</v>
       </c>
       <c r="F98">
-        <v>-2.052018623583998</v>
+        <v>-3.139491894672564</v>
       </c>
       <c r="G98">
-        <v>-3.201000764687528</v>
+        <v>-1.278746072675091</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.724933132167723</v>
       </c>
       <c r="E99">
-        <v>-47.13568367933436</v>
+        <v>-46.06671249740186</v>
       </c>
       <c r="F99">
-        <v>-2.741452245585971</v>
+        <v>-2.911167330704131</v>
       </c>
       <c r="G99">
-        <v>-3.480462697954068</v>
+        <v>-2.713264070920336</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.707596132593549</v>
       </c>
       <c r="E100">
-        <v>-49.33584218714812</v>
+        <v>-48.95360968929018</v>
       </c>
       <c r="F100">
-        <v>-2.593796584404362</v>
+        <v>-3.560271057333407</v>
       </c>
       <c r="G100">
-        <v>-3.888143519579363</v>
+        <v>-1.98606466176705</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.664181184341381</v>
       </c>
       <c r="E101">
-        <v>-50.63500925997057</v>
+        <v>-50.87519570070239</v>
       </c>
       <c r="F101">
-        <v>-2.897136443635512</v>
+        <v>-3.608199566891983</v>
       </c>
       <c r="G101">
-        <v>-4.668249667871559</v>
+        <v>-2.973926032386268</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.584075073900403</v>
       </c>
       <c r="E102">
-        <v>-52.64537846987365</v>
+        <v>-53.4827395924601</v>
       </c>
       <c r="F102">
-        <v>-3.241584863597992</v>
+        <v>-3.657730139007574</v>
       </c>
       <c r="G102">
-        <v>-6.58223613176394</v>
+        <v>-3.314698691630512</v>
       </c>
     </row>
   </sheetData>
